--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -18159,19 +18159,37 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1"/>
-      <c r="B529" s="1"/>
-      <c r="C529" s="1"/>
+      <c r="A529" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45995.0)</f>
+        <v>45995</v>
+      </c>
+      <c r="B529" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Picadinho")</f>
+        <v>Picadinho</v>
+      </c>
+      <c r="C529" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D529" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E529" s="1"/>
-      <c r="F529" s="1"/>
-      <c r="G529" s="1"/>
+      <c r="E529" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F529" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G529" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente alegou que o arroz estava ruim e o feijão duro e devolveu. Constatamos que procede a reclamação.")</f>
+        <v>Cliente alegou que o arroz estava ruim e o feijão duro e devolveu. Constatamos que procede a reclamação.</v>
+      </c>
       <c r="H529" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="530">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -18193,19 +18193,37 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1"/>
-      <c r="B530" s="1"/>
-      <c r="C530" s="1"/>
+      <c r="A530" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45996.0)</f>
+        <v>45996</v>
+      </c>
+      <c r="B530" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Salsa")</f>
+        <v>Salsa</v>
+      </c>
+      <c r="C530" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"73g")</f>
+        <v>73g</v>
+      </c>
       <c r="D530" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E530" s="1"/>
-      <c r="F530" s="1"/>
-      <c r="G530" s="1"/>
+      <c r="E530" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F530" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G530" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas amareladas. ")</f>
+        <v>Folhas amareladas. </v>
+      </c>
       <c r="H530" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="531">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -18164,8 +18164,8 @@
         <v>45995</v>
       </c>
       <c r="B529" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Picadinho")</f>
-        <v>Picadinho</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PICADINHO")</f>
+        <v>PICADINHO</v>
       </c>
       <c r="C529" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -18198,16 +18198,16 @@
         <v>45996</v>
       </c>
       <c r="B530" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Salsa")</f>
-        <v>Salsa</v>
-      </c>
-      <c r="C530" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"73g")</f>
-        <v>73g</v>
-      </c>
-      <c r="D530" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SALSA")</f>
+        <v>SALSA</v>
+      </c>
+      <c r="C530" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.73)</f>
+        <v>0.73</v>
+      </c>
+      <c r="D530" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9127)</f>
+        <v>2.9127</v>
       </c>
       <c r="E530" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
@@ -18227,83 +18227,173 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1"/>
-      <c r="B531" s="1"/>
-      <c r="C531" s="1"/>
-      <c r="D531" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E531" s="1"/>
-      <c r="F531" s="1"/>
-      <c r="G531" s="1"/>
+      <c r="A531" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B531" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TORTA LIMAO")</f>
+        <v>TORTA LIMAO</v>
+      </c>
+      <c r="C531" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D531" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.7299999999999995)</f>
+        <v>5.73</v>
+      </c>
+      <c r="E531" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F531" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EQUIPE")</f>
+        <v>EQUIPE</v>
+      </c>
+      <c r="G531" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Estava com água ")</f>
+        <v>Estava com água </v>
+      </c>
       <c r="H531" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1"/>
-      <c r="B532" s="1"/>
-      <c r="C532" s="1"/>
-      <c r="D532" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E532" s="1"/>
-      <c r="F532" s="1"/>
-      <c r="G532" s="1"/>
+      <c r="A532" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B532" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOLO TAPIOCA")</f>
+        <v>BOLO TAPIOCA</v>
+      </c>
+      <c r="C532" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D532" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.35)</f>
+        <v>10.35</v>
+      </c>
+      <c r="E532" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F532" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EQUIPE")</f>
+        <v>EQUIPE</v>
+      </c>
+      <c r="G532" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FATIA MUITO PEQUENA")</f>
+        <v>FATIA MUITO PEQUENA</v>
+      </c>
       <c r="H532" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1"/>
-      <c r="B533" s="1"/>
-      <c r="C533" s="1"/>
+      <c r="A533" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B533" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SHOT")</f>
+        <v>SHOT</v>
+      </c>
+      <c r="C533" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D533" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E533" s="1"/>
-      <c r="F533" s="1"/>
-      <c r="G533" s="1"/>
+      <c r="E533" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F533" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G533" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DEIXOU CAIR NA PIA")</f>
+        <v>DEIXOU CAIR NA PIA</v>
+      </c>
       <c r="H533" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1"/>
-      <c r="B534" s="1"/>
-      <c r="C534" s="1"/>
+      <c r="A534" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B534" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MACHIATO DUPLO")</f>
+        <v>MACHIATO DUPLO</v>
+      </c>
+      <c r="C534" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D534" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E534" s="1"/>
-      <c r="F534" s="1"/>
-      <c r="G534" s="1"/>
+      <c r="E534" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F534" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G534" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERA ESPRESSO DUPLO")</f>
+        <v>ERA ESPRESSO DUPLO</v>
+      </c>
       <c r="H534" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1"/>
-      <c r="B535" s="1"/>
-      <c r="C535" s="1"/>
-      <c r="D535" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E535" s="1"/>
-      <c r="F535" s="1"/>
-      <c r="G535" s="1"/>
+      <c r="A535" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B535" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPO PEQUENO")</f>
+        <v>COPO PEQUENO</v>
+      </c>
+      <c r="C535" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D535" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
+        <v>3.98</v>
+      </c>
+      <c r="E535" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F535" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G535" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RACHOU")</f>
+        <v>RACHOU</v>
+      </c>
       <c r="H535" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="536">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -17938,8 +17938,8 @@
         <v>0.06594</v>
       </c>
       <c r="E522" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
-        <v>Outro</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
       </c>
       <c r="F522" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
@@ -18006,8 +18006,8 @@
         <v>4.82</v>
       </c>
       <c r="E524" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de Processo")</f>
-        <v>Erro de Processo</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
       </c>
       <c r="F524" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
@@ -18164,8 +18164,8 @@
         <v>45995</v>
       </c>
       <c r="B529" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Picadinho")</f>
-        <v>Picadinho</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PICADINHO")</f>
+        <v>PICADINHO</v>
       </c>
       <c r="C529" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -18193,115 +18193,241 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1"/>
-      <c r="B530" s="1"/>
-      <c r="C530" s="1"/>
-      <c r="D530" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E530" s="1"/>
-      <c r="F530" s="1"/>
-      <c r="G530" s="1"/>
+      <c r="A530" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45996.0)</f>
+        <v>45996</v>
+      </c>
+      <c r="B530" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SALSA")</f>
+        <v>SALSA</v>
+      </c>
+      <c r="C530" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.73)</f>
+        <v>0.73</v>
+      </c>
+      <c r="D530" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9127)</f>
+        <v>2.9127</v>
+      </c>
+      <c r="E530" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F530" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G530" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas amareladas. ")</f>
+        <v>Folhas amareladas. </v>
+      </c>
       <c r="H530" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1"/>
-      <c r="B531" s="1"/>
-      <c r="C531" s="1"/>
-      <c r="D531" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E531" s="1"/>
-      <c r="F531" s="1"/>
-      <c r="G531" s="1"/>
+      <c r="A531" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B531" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TORTA LIMAO")</f>
+        <v>TORTA LIMAO</v>
+      </c>
+      <c r="C531" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D531" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.7299999999999995)</f>
+        <v>5.73</v>
+      </c>
+      <c r="E531" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F531" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EQUIPE")</f>
+        <v>EQUIPE</v>
+      </c>
+      <c r="G531" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Estava com água ")</f>
+        <v>Estava com água </v>
+      </c>
       <c r="H531" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1"/>
-      <c r="B532" s="1"/>
-      <c r="C532" s="1"/>
-      <c r="D532" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E532" s="1"/>
-      <c r="F532" s="1"/>
-      <c r="G532" s="1"/>
+      <c r="A532" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B532" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOLO TAPIOCA")</f>
+        <v>BOLO TAPIOCA</v>
+      </c>
+      <c r="C532" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D532" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.35)</f>
+        <v>10.35</v>
+      </c>
+      <c r="E532" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F532" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EQUIPE")</f>
+        <v>EQUIPE</v>
+      </c>
+      <c r="G532" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FATIA MUITO PEQUENA")</f>
+        <v>FATIA MUITO PEQUENA</v>
+      </c>
       <c r="H532" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1"/>
-      <c r="B533" s="1"/>
-      <c r="C533" s="1"/>
+      <c r="A533" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B533" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SHOT")</f>
+        <v>SHOT</v>
+      </c>
+      <c r="C533" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D533" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E533" s="1"/>
-      <c r="F533" s="1"/>
-      <c r="G533" s="1"/>
+      <c r="E533" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F533" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G533" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DEIXOU CAIR NA PIA")</f>
+        <v>DEIXOU CAIR NA PIA</v>
+      </c>
       <c r="H533" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1"/>
-      <c r="B534" s="1"/>
-      <c r="C534" s="1"/>
+      <c r="A534" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B534" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MACHIATO DUPLO")</f>
+        <v>MACHIATO DUPLO</v>
+      </c>
+      <c r="C534" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D534" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E534" s="1"/>
-      <c r="F534" s="1"/>
-      <c r="G534" s="1"/>
+      <c r="E534" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F534" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G534" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERA ESPRESSO DUPLO")</f>
+        <v>ERA ESPRESSO DUPLO</v>
+      </c>
       <c r="H534" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1"/>
-      <c r="B535" s="1"/>
-      <c r="C535" s="1"/>
-      <c r="D535" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E535" s="1"/>
-      <c r="F535" s="1"/>
-      <c r="G535" s="1"/>
+      <c r="A535" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
+        <v>45998</v>
+      </c>
+      <c r="B535" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPO PEQUENO")</f>
+        <v>COPO PEQUENO</v>
+      </c>
+      <c r="C535" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D535" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
+        <v>3.98</v>
+      </c>
+      <c r="E535" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F535" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G535" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RACHOU")</f>
+        <v>RACHOU</v>
+      </c>
       <c r="H535" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1"/>
-      <c r="B536" s="1"/>
-      <c r="C536" s="1"/>
+      <c r="A536" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45999.0)</f>
+        <v>45999</v>
+      </c>
+      <c r="B536" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Torta Ninho Trufado")</f>
+        <v>Torta Ninho Trufado</v>
+      </c>
+      <c r="C536" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D536" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E536" s="1"/>
-      <c r="F536" s="1"/>
-      <c r="G536" s="1"/>
+      <c r="E536" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F536" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESSYCA")</f>
+        <v>JESSYCA</v>
+      </c>
+      <c r="G536" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vencido.")</f>
+        <v>Vencido.</v>
+      </c>
       <c r="H536" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="537">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -18431,147 +18431,309 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1"/>
-      <c r="B537" s="1"/>
-      <c r="C537" s="1"/>
-      <c r="D537" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E537" s="1"/>
-      <c r="F537" s="1"/>
-      <c r="G537" s="1"/>
+      <c r="A537" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45999.0)</f>
+        <v>45999</v>
+      </c>
+      <c r="B537" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPO PEQUENO")</f>
+        <v>COPO PEQUENO</v>
+      </c>
+      <c r="C537" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D537" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
+        <v>3.98</v>
+      </c>
+      <c r="E537" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F537" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
+        <v>NAIANE</v>
+      </c>
+      <c r="G537" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"QUEBROU")</f>
+        <v>QUEBROU</v>
+      </c>
       <c r="H537" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1"/>
-      <c r="B538" s="1"/>
-      <c r="C538" s="1"/>
+      <c r="A538" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46000.0)</f>
+        <v>46000</v>
+      </c>
+      <c r="B538" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PRATO SOBREMESA ")</f>
+        <v>PRATO SOBREMESA </v>
+      </c>
+      <c r="C538" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D538" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E538" s="1"/>
-      <c r="F538" s="1"/>
-      <c r="G538" s="1"/>
+      <c r="E538" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F538" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G538" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DEIXOU CAIR ")</f>
+        <v>DEIXOU CAIR </v>
+      </c>
       <c r="H538" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1"/>
-      <c r="B539" s="1"/>
-      <c r="C539" s="1"/>
-      <c r="D539" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E539" s="1"/>
-      <c r="F539" s="1"/>
-      <c r="G539" s="1"/>
+      <c r="A539" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46000.0)</f>
+        <v>46000</v>
+      </c>
+      <c r="B539" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALFACE")</f>
+        <v>ALFACE</v>
+      </c>
+      <c r="C539" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.156)</f>
+        <v>0.156</v>
+      </c>
+      <c r="D539" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08888)</f>
+        <v>1.08888</v>
+      </c>
+      <c r="E539" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F539" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G539" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Amarelou")</f>
+        <v>Amarelou</v>
+      </c>
       <c r="H539" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1"/>
-      <c r="B540" s="1"/>
-      <c r="C540" s="1"/>
-      <c r="D540" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E540" s="1"/>
-      <c r="F540" s="1"/>
-      <c r="G540" s="1"/>
+      <c r="A540" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46000.0)</f>
+        <v>46000</v>
+      </c>
+      <c r="B540" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUCULA")</f>
+        <v>RUCULA</v>
+      </c>
+      <c r="C540" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.031)</f>
+        <v>0.031</v>
+      </c>
+      <c r="D540" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10509)</f>
+        <v>0.10509</v>
+      </c>
+      <c r="E540" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F540" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G540" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"estragou")</f>
+        <v>estragou</v>
+      </c>
       <c r="H540" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1"/>
-      <c r="B541" s="1"/>
-      <c r="C541" s="1"/>
+      <c r="A541" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46000.0)</f>
+        <v>46000</v>
+      </c>
+      <c r="B541" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MANJERICAO")</f>
+        <v>MANJERICAO</v>
+      </c>
+      <c r="C541" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.034)</f>
+        <v>0.034</v>
+      </c>
       <c r="D541" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E541" s="1"/>
-      <c r="F541" s="1"/>
-      <c r="G541" s="1"/>
+      <c r="E541" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F541" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G541" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"muchou")</f>
+        <v>muchou</v>
+      </c>
       <c r="H541" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1"/>
-      <c r="B542" s="1"/>
-      <c r="C542" s="1"/>
+      <c r="A542" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46000.0)</f>
+        <v>46000</v>
+      </c>
+      <c r="B542" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAO DE QUEIJO PORÇAO")</f>
+        <v>PAO DE QUEIJO PORÇAO</v>
+      </c>
+      <c r="C542" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="D542" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E542" s="1"/>
-      <c r="F542" s="1"/>
-      <c r="G542" s="1"/>
+      <c r="E542" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F542" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G542" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"mofou")</f>
+        <v>mofou</v>
+      </c>
       <c r="H542" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1"/>
-      <c r="B543" s="1"/>
-      <c r="C543" s="1"/>
+      <c r="A543" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46000.0)</f>
+        <v>46000</v>
+      </c>
+      <c r="B543" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAO DE QUEIJO UNIDADE")</f>
+        <v>PAO DE QUEIJO UNIDADE</v>
+      </c>
+      <c r="C543" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="D543" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E543" s="1"/>
-      <c r="F543" s="1"/>
-      <c r="G543" s="1"/>
+      <c r="E543" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F543" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G543" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"mofou")</f>
+        <v>mofou</v>
+      </c>
       <c r="H543" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1"/>
-      <c r="B544" s="1"/>
-      <c r="C544" s="1"/>
+      <c r="A544" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46000.0)</f>
+        <v>46000</v>
+      </c>
+      <c r="B544" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolo Maça")</f>
+        <v>Bolo Maça</v>
+      </c>
+      <c r="C544" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D544" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E544" s="1"/>
-      <c r="F544" s="1"/>
-      <c r="G544" s="1"/>
+      <c r="E544" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F544" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G544" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Entrou água da geladeira no bolo.")</f>
+        <v>Entrou água da geladeira no bolo.</v>
+      </c>
       <c r="H544" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1"/>
-      <c r="B545" s="1"/>
-      <c r="C545" s="1"/>
-      <c r="D545" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E545" s="1"/>
-      <c r="F545" s="1"/>
-      <c r="G545" s="1"/>
+      <c r="A545" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46001.0)</f>
+        <v>46001</v>
+      </c>
+      <c r="B545" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Petit Gateau")</f>
+        <v>Petit Gateau</v>
+      </c>
+      <c r="C545" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D545" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="E545" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F545" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
+        <v>NAIANE</v>
+      </c>
+      <c r="G545" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu na vtitrine.")</f>
+        <v>Venceu na vtitrine.</v>
+      </c>
       <c r="H545" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="546">
@@ -28034,7 +28196,10 @@
       <c r="A1137" s="1"/>
       <c r="B1137" s="1"/>
       <c r="C1137" s="1"/>
-      <c r="D1137" s="1"/>
+      <c r="D1137" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
+      </c>
       <c r="E1137" s="1"/>
       <c r="F1137" s="1"/>
       <c r="G1137" s="1"/>
@@ -28051,7 +28216,10 @@
       <c r="E1138" s="1"/>
       <c r="F1138" s="1"/>
       <c r="G1138" s="1"/>
-      <c r="H1138" s="1"/>
+      <c r="H1138" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="1139">
       <c r="A1139" s="1"/>
@@ -28103,6 +28271,16 @@
       <c r="G1143" s="1"/>
       <c r="H1143" s="1"/>
     </row>
+    <row r="1144">
+      <c r="A1144" s="1"/>
+      <c r="B1144" s="1"/>
+      <c r="C1144" s="1"/>
+      <c r="D1144" s="1"/>
+      <c r="E1144" s="1"/>
+      <c r="F1144" s="1"/>
+      <c r="G1144" s="1"/>
+      <c r="H1144" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -18737,19 +18737,37 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1"/>
-      <c r="B546" s="1"/>
-      <c r="C546" s="1"/>
+      <c r="A546" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46002.0)</f>
+        <v>46002</v>
+      </c>
+      <c r="B546" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"tomate")</f>
+        <v>tomate</v>
+      </c>
+      <c r="C546" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),",031 g")</f>
+        <v>,031 g</v>
+      </c>
       <c r="D546" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E546" s="1"/>
-      <c r="F546" s="1"/>
-      <c r="G546" s="1"/>
+      <c r="E546" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F546" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G546" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"passada")</f>
+        <v>passada</v>
+      </c>
       <c r="H546" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="547">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -18771,35 +18771,71 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1"/>
-      <c r="B547" s="1"/>
-      <c r="C547" s="1"/>
+      <c r="A547" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46003.0)</f>
+        <v>46003</v>
+      </c>
+      <c r="B547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface")</f>
+        <v>Alface</v>
+      </c>
+      <c r="C547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"110g")</f>
+        <v>110g</v>
+      </c>
       <c r="D547" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E547" s="1"/>
-      <c r="F547" s="1"/>
-      <c r="G547" s="1"/>
+      <c r="E547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
+        <v>NAIANE</v>
+      </c>
+      <c r="G547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas amareladas")</f>
+        <v>Folhas amareladas</v>
+      </c>
       <c r="H547" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1"/>
-      <c r="B548" s="1"/>
-      <c r="C548" s="1"/>
+      <c r="A548" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46003.0)</f>
+        <v>46003</v>
+      </c>
+      <c r="B548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Queijo Brie")</f>
+        <v>Queijo Brie</v>
+      </c>
+      <c r="C548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"11g")</f>
+        <v>11g</v>
+      </c>
       <c r="D548" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E548" s="1"/>
-      <c r="F548" s="1"/>
-      <c r="G548" s="1"/>
+      <c r="E548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
+        <v>NAIANE</v>
+      </c>
+      <c r="G548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu")</f>
+        <v>Venceu</v>
+      </c>
       <c r="H548" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="549">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -18771,83 +18771,173 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1"/>
-      <c r="B547" s="1"/>
-      <c r="C547" s="1"/>
+      <c r="A547" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46003.0)</f>
+        <v>46003</v>
+      </c>
+      <c r="B547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface")</f>
+        <v>Alface</v>
+      </c>
+      <c r="C547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"110g")</f>
+        <v>110g</v>
+      </c>
       <c r="D547" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E547" s="1"/>
-      <c r="F547" s="1"/>
-      <c r="G547" s="1"/>
+      <c r="E547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
+        <v>NAIANE</v>
+      </c>
+      <c r="G547" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas amareladas")</f>
+        <v>Folhas amareladas</v>
+      </c>
       <c r="H547" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1"/>
-      <c r="B548" s="1"/>
-      <c r="C548" s="1"/>
+      <c r="A548" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46003.0)</f>
+        <v>46003</v>
+      </c>
+      <c r="B548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Queijo Brie")</f>
+        <v>Queijo Brie</v>
+      </c>
+      <c r="C548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"11g")</f>
+        <v>11g</v>
+      </c>
       <c r="D548" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E548" s="1"/>
-      <c r="F548" s="1"/>
-      <c r="G548" s="1"/>
+      <c r="E548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
+        <v>NAIANE</v>
+      </c>
+      <c r="G548" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu")</f>
+        <v>Venceu</v>
+      </c>
       <c r="H548" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1"/>
-      <c r="B549" s="1"/>
-      <c r="C549" s="1"/>
+      <c r="A549" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46004.0)</f>
+        <v>46004</v>
+      </c>
+      <c r="B549" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Leite vegetal")</f>
+        <v>Leite vegetal</v>
+      </c>
+      <c r="C549" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"2 litros")</f>
+        <v>2 litros</v>
+      </c>
       <c r="D549" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E549" s="1"/>
-      <c r="F549" s="1"/>
-      <c r="G549" s="1"/>
+      <c r="E549" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F549" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX")</f>
+        <v>ALEX</v>
+      </c>
+      <c r="G549" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Problema de qualidade")</f>
+        <v>Problema de qualidade</v>
+      </c>
       <c r="H549" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1"/>
-      <c r="B550" s="1"/>
-      <c r="C550" s="1"/>
-      <c r="D550" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E550" s="1"/>
-      <c r="F550" s="1"/>
-      <c r="G550" s="1"/>
+      <c r="A550" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46004.0)</f>
+        <v>46004</v>
+      </c>
+      <c r="B550" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo pequeno")</f>
+        <v>Copo pequeno</v>
+      </c>
+      <c r="C550" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D550" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
+        <v>3.98</v>
+      </c>
+      <c r="E550" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F550" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GABRIELA")</f>
+        <v>GABRIELA</v>
+      </c>
+      <c r="G550" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Deixou cair")</f>
+        <v>Deixou cair</v>
+      </c>
       <c r="H550" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1"/>
-      <c r="B551" s="1"/>
-      <c r="C551" s="1"/>
+      <c r="A551" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46004.0)</f>
+        <v>46004</v>
+      </c>
+      <c r="B551" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Risoto Funghi")</f>
+        <v>Risoto Funghi</v>
+      </c>
+      <c r="C551" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D551" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E551" s="1"/>
-      <c r="F551" s="1"/>
-      <c r="G551" s="1"/>
+      <c r="E551" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F551" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX")</f>
+        <v>ALEX</v>
+      </c>
+      <c r="G551" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente alega ter encontrado uma pedra no risoto. Tiramos uma foto para sinalizar o fornecedor.")</f>
+        <v>Cliente alega ter encontrado uma pedra no risoto. Tiramos uma foto para sinalizar o fornecedor.</v>
+      </c>
       <c r="H551" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="552">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -18941,51 +18941,105 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1"/>
-      <c r="B552" s="1"/>
-      <c r="C552" s="1"/>
+      <c r="A552" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46006.0)</f>
+        <v>46006</v>
+      </c>
+      <c r="B552" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"tomate")</f>
+        <v>tomate</v>
+      </c>
+      <c r="C552" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,03g")</f>
+        <v>0,03g</v>
+      </c>
       <c r="D552" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E552" s="1"/>
-      <c r="F552" s="1"/>
-      <c r="G552" s="1"/>
+      <c r="E552" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F552" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G552" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"estragou")</f>
+        <v>estragou</v>
+      </c>
       <c r="H552" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1"/>
-      <c r="B553" s="1"/>
-      <c r="C553" s="1"/>
+      <c r="A553" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46006.0)</f>
+        <v>46006</v>
+      </c>
+      <c r="B553" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"rucula")</f>
+        <v>rucula</v>
+      </c>
+      <c r="C553" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,217g")</f>
+        <v>0,217g</v>
+      </c>
       <c r="D553" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E553" s="1"/>
-      <c r="F553" s="1"/>
-      <c r="G553" s="1"/>
+      <c r="E553" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F553" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G553" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"amarelou")</f>
+        <v>amarelou</v>
+      </c>
       <c r="H553" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1"/>
-      <c r="B554" s="1"/>
-      <c r="C554" s="1"/>
-      <c r="D554" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E554" s="1"/>
-      <c r="F554" s="1"/>
-      <c r="G554" s="1"/>
+      <c r="A554" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46006.0)</f>
+        <v>46006</v>
+      </c>
+      <c r="B554" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"manjericao")</f>
+        <v>manjericao</v>
+      </c>
+      <c r="C554" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.041)</f>
+        <v>0.041</v>
+      </c>
+      <c r="D554" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6318)</f>
+        <v>1.6318</v>
+      </c>
+      <c r="E554" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F554" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G554" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"murchou")</f>
+        <v>murchou</v>
+      </c>
       <c r="H554" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="555">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19043,19 +19043,37 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1"/>
-      <c r="B555" s="1"/>
-      <c r="C555" s="1"/>
-      <c r="D555" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E555" s="1"/>
-      <c r="F555" s="1"/>
-      <c r="G555" s="1"/>
+      <c r="A555" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46007.0)</f>
+        <v>46007</v>
+      </c>
+      <c r="B555" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATCHA GELADO")</f>
+        <v>MATCHA GELADO</v>
+      </c>
+      <c r="C555" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D555" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.71)</f>
+        <v>5.71</v>
+      </c>
+      <c r="E555" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="F555" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G555" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"cliente nao quis mais")</f>
+        <v>cliente nao quis mais</v>
+      </c>
       <c r="H555" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="556">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -17751,7 +17751,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
         <v>100</v>
       </c>
-      <c r="E516" s="1"/>
+      <c r="E516" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
       <c r="F516" s="1"/>
       <c r="G516" s="1"/>
       <c r="H516" s="1" t="str">
@@ -17776,7 +17779,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E517" s="1"/>
+      <c r="E517" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
       <c r="F517" s="1"/>
       <c r="G517" s="1"/>
       <c r="H517" s="1" t="str">
@@ -18958,8 +18964,8 @@
         <v/>
       </c>
       <c r="E552" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
-        <v>Outro</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
       </c>
       <c r="F552" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
@@ -18992,8 +18998,8 @@
         <v/>
       </c>
       <c r="E553" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
-        <v>Outro</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
       </c>
       <c r="F553" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
@@ -19026,8 +19032,8 @@
         <v>1.6318</v>
       </c>
       <c r="E554" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
-        <v>Outro</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
       </c>
       <c r="F554" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
@@ -19077,19 +19083,37 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1"/>
-      <c r="B556" s="1"/>
-      <c r="C556" s="1"/>
+      <c r="A556" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46008.0)</f>
+        <v>46008</v>
+      </c>
+      <c r="B556" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manjericão")</f>
+        <v>Manjericão</v>
+      </c>
+      <c r="C556" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"200gr")</f>
+        <v>200gr</v>
+      </c>
       <c r="D556" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E556" s="1"/>
-      <c r="F556" s="1"/>
-      <c r="G556" s="1"/>
+      <c r="E556" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F556" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G556" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Murchou")</f>
+        <v>Murchou</v>
+      </c>
       <c r="H556" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="557">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19117,35 +19117,71 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1"/>
-      <c r="B557" s="1"/>
-      <c r="C557" s="1"/>
+      <c r="A557" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46010.0)</f>
+        <v>46010</v>
+      </c>
+      <c r="B557" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pão de batata")</f>
+        <v>Pão de batata</v>
+      </c>
+      <c r="C557" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D557" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E557" s="1"/>
-      <c r="F557" s="1"/>
-      <c r="G557" s="1"/>
+      <c r="E557" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F557" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX")</f>
+        <v>ALEX</v>
+      </c>
+      <c r="G557" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Separado para prova a pedido do Renan ")</f>
+        <v>Separado para prova a pedido do Renan </v>
+      </c>
       <c r="H557" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1"/>
-      <c r="B558" s="1"/>
-      <c r="C558" s="1"/>
+      <c r="A558" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46010.0)</f>
+        <v>46010</v>
+      </c>
+      <c r="B558" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Brigadeiro premium")</f>
+        <v>Brigadeiro premium</v>
+      </c>
+      <c r="C558" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="D558" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E558" s="1"/>
-      <c r="F558" s="1"/>
-      <c r="G558" s="1"/>
+      <c r="E558" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F558" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX")</f>
+        <v>ALEX</v>
+      </c>
+      <c r="G558" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vencido. ")</f>
+        <v>Vencido. </v>
+      </c>
       <c r="H558" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="559">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19185,115 +19185,241 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1"/>
-      <c r="B559" s="1"/>
-      <c r="C559" s="1"/>
-      <c r="D559" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E559" s="1"/>
-      <c r="F559" s="1"/>
-      <c r="G559" s="1"/>
+      <c r="A559" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46011.0)</f>
+        <v>46011</v>
+      </c>
+      <c r="B559" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Palha italiana")</f>
+        <v>Palha italiana</v>
+      </c>
+      <c r="C559" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="D559" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.7)</f>
+        <v>20.7</v>
+      </c>
+      <c r="E559" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F559" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX")</f>
+        <v>ALEX</v>
+      </c>
+      <c r="G559" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prova - Autorizado Brunna")</f>
+        <v>Prova - Autorizado Brunna</v>
+      </c>
       <c r="H559" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1"/>
-      <c r="B560" s="1"/>
-      <c r="C560" s="1"/>
-      <c r="D560" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E560" s="1"/>
-      <c r="F560" s="1"/>
-      <c r="G560" s="1"/>
+      <c r="A560" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46011.0)</f>
+        <v>46011</v>
+      </c>
+      <c r="B560" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAPPUCCINO ITALIANO")</f>
+        <v>CAPPUCCINO ITALIANO</v>
+      </c>
+      <c r="C560" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D560" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.71)</f>
+        <v>2.71</v>
+      </c>
+      <c r="E560" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de Processo")</f>
+        <v>Erro de Processo</v>
+      </c>
+      <c r="F560" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESSYCA")</f>
+        <v>JESSYCA</v>
+      </c>
+      <c r="G560" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEZ ERRADO")</f>
+        <v>FEZ ERRADO</v>
+      </c>
       <c r="H560" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1"/>
-      <c r="B561" s="1"/>
-      <c r="C561" s="1"/>
-      <c r="D561" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E561" s="1"/>
-      <c r="F561" s="1"/>
-      <c r="G561" s="1"/>
+      <c r="A561" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46011.0)</f>
+        <v>46011</v>
+      </c>
+      <c r="B561" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COXINHA")</f>
+        <v>COXINHA</v>
+      </c>
+      <c r="C561" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D561" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="E561" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="F561" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G561" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SE ABRIU")</f>
+        <v>SE ABRIU</v>
+      </c>
       <c r="H561" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1"/>
-      <c r="B562" s="1"/>
-      <c r="C562" s="1"/>
-      <c r="D562" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E562" s="1"/>
-      <c r="F562" s="1"/>
-      <c r="G562" s="1"/>
+      <c r="A562" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46011.0)</f>
+        <v>46011</v>
+      </c>
+      <c r="B562" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOLO TAPIOCA")</f>
+        <v>BOLO TAPIOCA</v>
+      </c>
+      <c r="C562" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D562" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.35)</f>
+        <v>10.35</v>
+      </c>
+      <c r="E562" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de Processo")</f>
+        <v>Erro de Processo</v>
+      </c>
+      <c r="F562" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
+        <v>NAIANE</v>
+      </c>
+      <c r="G562" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FATIA PEQUENA")</f>
+        <v>FATIA PEQUENA</v>
+      </c>
       <c r="H562" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1"/>
-      <c r="B563" s="1"/>
-      <c r="C563" s="1"/>
-      <c r="D563" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E563" s="1"/>
-      <c r="F563" s="1"/>
-      <c r="G563" s="1"/>
+      <c r="A563" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46012.0)</f>
+        <v>46012</v>
+      </c>
+      <c r="B563" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPO GRANDE")</f>
+        <v>COPO GRANDE</v>
+      </c>
+      <c r="C563" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D563" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="E563" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F563" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GABRIELA")</f>
+        <v>GABRIELA</v>
+      </c>
+      <c r="G563" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"deixou cair na louça")</f>
+        <v>deixou cair na louça</v>
+      </c>
       <c r="H563" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1"/>
-      <c r="B564" s="1"/>
-      <c r="C564" s="1"/>
-      <c r="D564" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E564" s="1"/>
-      <c r="F564" s="1"/>
-      <c r="G564" s="1"/>
+      <c r="A564" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46012.0)</f>
+        <v>46012</v>
+      </c>
+      <c r="B564" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"rucula")</f>
+        <v>rucula</v>
+      </c>
+      <c r="C564" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.014)</f>
+        <v>0.014</v>
+      </c>
+      <c r="D564" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.04746)</f>
+        <v>0.04746</v>
+      </c>
+      <c r="E564" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F564" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G564" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"amarelou")</f>
+        <v>amarelou</v>
+      </c>
       <c r="H564" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1"/>
-      <c r="B565" s="1"/>
-      <c r="C565" s="1"/>
-      <c r="D565" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E565" s="1"/>
-      <c r="F565" s="1"/>
-      <c r="G565" s="1"/>
+      <c r="A565" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46012.0)</f>
+        <v>46012</v>
+      </c>
+      <c r="B565" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OVO")</f>
+        <v>OVO</v>
+      </c>
+      <c r="C565" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D565" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.71)</f>
+        <v>0.71</v>
+      </c>
+      <c r="E565" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F565" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G565" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PODRE")</f>
+        <v>PODRE</v>
+      </c>
       <c r="H565" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="566">
@@ -28404,10 +28530,7 @@
       <c r="A1135" s="1"/>
       <c r="B1135" s="1"/>
       <c r="C1135" s="1"/>
-      <c r="D1135" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
+      <c r="D1135" s="1"/>
       <c r="E1135" s="1"/>
       <c r="F1135" s="1"/>
       <c r="G1135" s="1"/>
@@ -28420,33 +28543,21 @@
       <c r="A1136" s="1"/>
       <c r="B1136" s="1"/>
       <c r="C1136" s="1"/>
-      <c r="D1136" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
+      <c r="D1136" s="1"/>
       <c r="E1136" s="1"/>
       <c r="F1136" s="1"/>
       <c r="G1136" s="1"/>
-      <c r="H1136" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
+      <c r="H1136" s="1"/>
     </row>
     <row r="1137">
       <c r="A1137" s="1"/>
       <c r="B1137" s="1"/>
       <c r="C1137" s="1"/>
-      <c r="D1137" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
+      <c r="D1137" s="1"/>
       <c r="E1137" s="1"/>
       <c r="F1137" s="1"/>
       <c r="G1137" s="1"/>
-      <c r="H1137" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
+      <c r="H1137" s="1"/>
     </row>
     <row r="1138">
       <c r="A1138" s="1"/>
@@ -28456,10 +28567,7 @@
       <c r="E1138" s="1"/>
       <c r="F1138" s="1"/>
       <c r="G1138" s="1"/>
-      <c r="H1138" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
+      <c r="H1138" s="1"/>
     </row>
     <row r="1139">
       <c r="A1139" s="1"/>
@@ -28491,36 +28599,6 @@
       <c r="G1141" s="1"/>
       <c r="H1141" s="1"/>
     </row>
-    <row r="1142">
-      <c r="A1142" s="1"/>
-      <c r="B1142" s="1"/>
-      <c r="C1142" s="1"/>
-      <c r="D1142" s="1"/>
-      <c r="E1142" s="1"/>
-      <c r="F1142" s="1"/>
-      <c r="G1142" s="1"/>
-      <c r="H1142" s="1"/>
-    </row>
-    <row r="1143">
-      <c r="A1143" s="1"/>
-      <c r="B1143" s="1"/>
-      <c r="C1143" s="1"/>
-      <c r="D1143" s="1"/>
-      <c r="E1143" s="1"/>
-      <c r="F1143" s="1"/>
-      <c r="G1143" s="1"/>
-      <c r="H1143" s="1"/>
-    </row>
-    <row r="1144">
-      <c r="A1144" s="1"/>
-      <c r="B1144" s="1"/>
-      <c r="C1144" s="1"/>
-      <c r="D1144" s="1"/>
-      <c r="E1144" s="1"/>
-      <c r="F1144" s="1"/>
-      <c r="G1144" s="1"/>
-      <c r="H1144" s="1"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19236,8 +19236,8 @@
         <v>2.71</v>
       </c>
       <c r="E560" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de Processo")</f>
-        <v>Erro de Processo</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
       </c>
       <c r="F560" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESSYCA")</f>
@@ -19304,8 +19304,8 @@
         <v>10.35</v>
       </c>
       <c r="E562" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de Processo")</f>
-        <v>Erro de Processo</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
       </c>
       <c r="F562" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19423,19 +19423,37 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1"/>
-      <c r="B566" s="1"/>
-      <c r="C566" s="1"/>
-      <c r="D566" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E566" s="1"/>
-      <c r="F566" s="1"/>
-      <c r="G566" s="1"/>
+      <c r="A566" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46013.0)</f>
+        <v>46013</v>
+      </c>
+      <c r="B566" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo grande")</f>
+        <v>Copo grande</v>
+      </c>
+      <c r="C566" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D566" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="E566" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F566" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX")</f>
+        <v>ALEX</v>
+      </c>
+      <c r="G566" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente quebrou na mesa")</f>
+        <v>Cliente quebrou na mesa</v>
+      </c>
       <c r="H566" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="567">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19457,83 +19457,173 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1"/>
-      <c r="B567" s="1"/>
-      <c r="C567" s="1"/>
-      <c r="D567" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E567" s="1"/>
-      <c r="F567" s="1"/>
-      <c r="G567" s="1"/>
+      <c r="A567" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46014.0)</f>
+        <v>46014</v>
+      </c>
+      <c r="B567" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface")</f>
+        <v>Alface</v>
+      </c>
+      <c r="C567" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.109)</f>
+        <v>0.109</v>
+      </c>
+      <c r="D567" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.76082)</f>
+        <v>0.76082</v>
+      </c>
+      <c r="E567" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F567" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G567" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas amareladas")</f>
+        <v>Folhas amareladas</v>
+      </c>
       <c r="H567" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1"/>
-      <c r="B568" s="1"/>
-      <c r="C568" s="1"/>
-      <c r="D568" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E568" s="1"/>
-      <c r="F568" s="1"/>
-      <c r="G568" s="1"/>
+      <c r="A568" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46014.0)</f>
+        <v>46014</v>
+      </c>
+      <c r="B568" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pão ciabata")</f>
+        <v>Pão ciabata</v>
+      </c>
+      <c r="C568" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D568" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="E568" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F568" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G568" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cortado errado (fatia fina)")</f>
+        <v>Cortado errado (fatia fina)</v>
+      </c>
       <c r="H568" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1"/>
-      <c r="B569" s="1"/>
-      <c r="C569" s="1"/>
+      <c r="A569" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46014.0)</f>
+        <v>46014</v>
+      </c>
+      <c r="B569" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolo Maça")</f>
+        <v>Bolo Maça</v>
+      </c>
+      <c r="C569" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D569" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E569" s="1"/>
-      <c r="F569" s="1"/>
-      <c r="G569" s="1"/>
+      <c r="E569" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F569" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G569" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Última fatia pequena")</f>
+        <v>Última fatia pequena</v>
+      </c>
       <c r="H569" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1"/>
-      <c r="B570" s="1"/>
-      <c r="C570" s="1"/>
-      <c r="D570" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E570" s="1"/>
-      <c r="F570" s="1"/>
-      <c r="G570" s="1"/>
+      <c r="A570" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46014.0)</f>
+        <v>46014</v>
+      </c>
+      <c r="B570" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Queijo Minas")</f>
+        <v>Queijo Minas</v>
+      </c>
+      <c r="C570" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.021)</f>
+        <v>0.021</v>
+      </c>
+      <c r="D570" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2159)</f>
+        <v>1.2159</v>
+      </c>
+      <c r="E570" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F570" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESIANA")</f>
+        <v>JESIANA</v>
+      </c>
+      <c r="G570" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vencido")</f>
+        <v>Vencido</v>
+      </c>
       <c r="H570" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1"/>
-      <c r="B571" s="1"/>
-      <c r="C571" s="1"/>
-      <c r="D571" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E571" s="1"/>
-      <c r="F571" s="1"/>
-      <c r="G571" s="1"/>
+      <c r="A571" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46016.0)</f>
+        <v>46016</v>
+      </c>
+      <c r="B571" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ovo")</f>
+        <v>ovo</v>
+      </c>
+      <c r="C571" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D571" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.71)</f>
+        <v>0.71</v>
+      </c>
+      <c r="E571" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F571" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G571" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"podre")</f>
+        <v>podre</v>
+      </c>
       <c r="H571" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="572">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19627,35 +19627,71 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1"/>
-      <c r="B572" s="1"/>
-      <c r="C572" s="1"/>
-      <c r="D572" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E572" s="1"/>
-      <c r="F572" s="1"/>
-      <c r="G572" s="1"/>
+      <c r="A572" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46017.0)</f>
+        <v>46017</v>
+      </c>
+      <c r="B572" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Empada palmito")</f>
+        <v>Empada palmito</v>
+      </c>
+      <c r="C572" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="D572" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
+      </c>
+      <c r="E572" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F572" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
+        <v>NAIANE</v>
+      </c>
+      <c r="G572" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vencido (tempo de vitrine)")</f>
+        <v>Vencido (tempo de vitrine)</v>
+      </c>
       <c r="H572" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1"/>
-      <c r="B573" s="1"/>
-      <c r="C573" s="1"/>
+      <c r="A573" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46017.0)</f>
+        <v>46017</v>
+      </c>
+      <c r="B573" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Brownie")</f>
+        <v>Brownie</v>
+      </c>
+      <c r="C573" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D573" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E573" s="1"/>
-      <c r="F573" s="1"/>
-      <c r="G573" s="1"/>
+      <c r="E573" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F573" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAIANE")</f>
+        <v>NAIANE</v>
+      </c>
+      <c r="G573" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vencido (tempo de vitrine)")</f>
+        <v>Vencido (tempo de vitrine)</v>
+      </c>
       <c r="H573" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="574">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19695,19 +19695,37 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1"/>
-      <c r="B574" s="1"/>
-      <c r="C574" s="1"/>
+      <c r="A574" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46018.0)</f>
+        <v>46018</v>
+      </c>
+      <c r="B574" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"shot")</f>
+        <v>shot</v>
+      </c>
+      <c r="C574" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D574" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E574" s="1"/>
-      <c r="F574" s="1"/>
-      <c r="G574" s="1"/>
+      <c r="E574" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F574" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
+        <v>FABIO</v>
+      </c>
+      <c r="G574" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"escorregou da mao")</f>
+        <v>escorregou da mao</v>
+      </c>
       <c r="H574" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="575">
@@ -28642,10 +28660,7 @@
       <c r="A1133" s="1"/>
       <c r="B1133" s="1"/>
       <c r="C1133" s="1"/>
-      <c r="D1133" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
+      <c r="D1133" s="1"/>
       <c r="E1133" s="1"/>
       <c r="F1133" s="1"/>
       <c r="G1133" s="1"/>
@@ -28658,17 +28673,11 @@
       <c r="A1134" s="1"/>
       <c r="B1134" s="1"/>
       <c r="C1134" s="1"/>
-      <c r="D1134" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
+      <c r="D1134" s="1"/>
       <c r="E1134" s="1"/>
       <c r="F1134" s="1"/>
       <c r="G1134" s="1"/>
-      <c r="H1134" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
+      <c r="H1134" s="1"/>
     </row>
     <row r="1135">
       <c r="A1135" s="1"/>
@@ -28678,10 +28687,7 @@
       <c r="E1135" s="1"/>
       <c r="F1135" s="1"/>
       <c r="G1135" s="1"/>
-      <c r="H1135" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
+      <c r="H1135" s="1"/>
     </row>
     <row r="1136">
       <c r="A1136" s="1"/>
@@ -28723,26 +28729,6 @@
       <c r="G1139" s="1"/>
       <c r="H1139" s="1"/>
     </row>
-    <row r="1140">
-      <c r="A1140" s="1"/>
-      <c r="B1140" s="1"/>
-      <c r="C1140" s="1"/>
-      <c r="D1140" s="1"/>
-      <c r="E1140" s="1"/>
-      <c r="F1140" s="1"/>
-      <c r="G1140" s="1"/>
-      <c r="H1140" s="1"/>
-    </row>
-    <row r="1141">
-      <c r="A1141" s="1"/>
-      <c r="B1141" s="1"/>
-      <c r="C1141" s="1"/>
-      <c r="D1141" s="1"/>
-      <c r="E1141" s="1"/>
-      <c r="F1141" s="1"/>
-      <c r="G1141" s="1"/>
-      <c r="H1141" s="1"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19712,8 +19712,8 @@
         <v/>
       </c>
       <c r="E574" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
-        <v>Quebra</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
       </c>
       <c r="F574" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIO")</f>
@@ -19729,51 +19729,105 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1"/>
-      <c r="B575" s="1"/>
-      <c r="C575" s="1"/>
+      <c r="A575" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46020.0)</f>
+        <v>46020</v>
+      </c>
+      <c r="B575" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"porcao pao de queijo")</f>
+        <v>porcao pao de queijo</v>
+      </c>
+      <c r="C575" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="D575" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E575" s="1"/>
-      <c r="F575" s="1"/>
-      <c r="G575" s="1"/>
+      <c r="E575" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F575" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G575" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"passado")</f>
+        <v>passado</v>
+      </c>
       <c r="H575" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1"/>
-      <c r="B576" s="1"/>
-      <c r="C576" s="1"/>
+      <c r="A576" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46020.0)</f>
+        <v>46020</v>
+      </c>
+      <c r="B576" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"unidade pao de quejo")</f>
+        <v>unidade pao de quejo</v>
+      </c>
+      <c r="C576" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="D576" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E576" s="1"/>
-      <c r="F576" s="1"/>
-      <c r="G576" s="1"/>
+      <c r="E576" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F576" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G576" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"passado")</f>
+        <v>passado</v>
+      </c>
       <c r="H576" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1"/>
-      <c r="B577" s="1"/>
-      <c r="C577" s="1"/>
-      <c r="D577" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E577" s="1"/>
-      <c r="F577" s="1"/>
-      <c r="G577" s="1"/>
+      <c r="A577" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46020.0)</f>
+        <v>46020</v>
+      </c>
+      <c r="B577" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ovo")</f>
+        <v>ovo</v>
+      </c>
+      <c r="C577" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="D577" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.13)</f>
+        <v>2.13</v>
+      </c>
+      <c r="E577" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F577" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COZINHA")</f>
+        <v>COZINHA</v>
+      </c>
+      <c r="G577" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"podre")</f>
+        <v>podre</v>
+      </c>
       <c r="H577" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="578">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19831,19 +19831,34 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1"/>
-      <c r="B578" s="1"/>
-      <c r="C578" s="1"/>
-      <c r="D578" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E578" s="1"/>
-      <c r="F578" s="1"/>
+      <c r="A578" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46021.0)</f>
+        <v>46021</v>
+      </c>
+      <c r="B578" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo pequeno")</f>
+        <v>Copo pequeno</v>
+      </c>
+      <c r="C578" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D578" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
+        <v>3.98</v>
+      </c>
+      <c r="E578" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F578" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JESSYCA")</f>
+        <v>JESSYCA</v>
+      </c>
       <c r="G578" s="1"/>
       <c r="H578" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/2025")</f>
+        <v>12/2025</v>
       </c>
     </row>
     <row r="579">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19862,35 +19862,71 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1"/>
-      <c r="B579" s="1"/>
-      <c r="C579" s="1"/>
-      <c r="D579" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E579" s="1"/>
-      <c r="F579" s="1"/>
-      <c r="G579" s="1"/>
+      <c r="A579" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46024.0)</f>
+        <v>46024</v>
+      </c>
+      <c r="B579" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo pequeno")</f>
+        <v>Copo pequeno</v>
+      </c>
+      <c r="C579" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D579" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
+        <v>3.98</v>
+      </c>
+      <c r="E579" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F579" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAQUELINE")</f>
+        <v>JAQUELINE</v>
+      </c>
+      <c r="G579" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Encontrado quebrado em baixo do caixa")</f>
+        <v>Encontrado quebrado em baixo do caixa</v>
+      </c>
       <c r="H579" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01/2025")</f>
+        <v>01/2025</v>
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1"/>
-      <c r="B580" s="1"/>
-      <c r="C580" s="1"/>
-      <c r="D580" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E580" s="1"/>
-      <c r="F580" s="1"/>
-      <c r="G580" s="1"/>
+      <c r="A580" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46024.0)</f>
+        <v>46024</v>
+      </c>
+      <c r="B580" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo shot")</f>
+        <v>Copo shot</v>
+      </c>
+      <c r="C580" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D580" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.35)</f>
+        <v>2.35</v>
+      </c>
+      <c r="E580" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F580" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAQUELINE")</f>
+        <v>JAQUELINE</v>
+      </c>
+      <c r="G580" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Lascado na bandeja")</f>
+        <v>Lascado na bandeja</v>
+      </c>
       <c r="H580" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01/2025")</f>
+        <v>01/2025</v>
       </c>
     </row>
     <row r="581">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -7016,8 +7016,8 @@
     </row>
     <row r="200">
       <c r="A200" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46171.0)</f>
-        <v>46171</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45806.0)</f>
+        <v>45806</v>
       </c>
       <c r="B200" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUCULA")</f>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19930,19 +19930,34 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1"/>
-      <c r="B581" s="1"/>
-      <c r="C581" s="1"/>
-      <c r="D581" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="E581" s="1"/>
-      <c r="F581" s="1"/>
+      <c r="A581" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46026.0)</f>
+        <v>46026</v>
+      </c>
+      <c r="B581" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo shot")</f>
+        <v>Copo shot</v>
+      </c>
+      <c r="C581" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D581" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.35)</f>
+        <v>2.35</v>
+      </c>
+      <c r="E581" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F581" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAQUELINE")</f>
+        <v>JAQUELINE</v>
+      </c>
       <c r="G581" s="1"/>
       <c r="H581" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01/2025")</f>
+        <v>01/2025</v>
       </c>
     </row>
     <row r="582">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -19961,19 +19961,34 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1"/>
-      <c r="B582" s="1"/>
-      <c r="C582" s="1"/>
+      <c r="A582" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46029.0)</f>
+        <v>46029</v>
+      </c>
+      <c r="B582" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Taça de vinho")</f>
+        <v>Taça de vinho</v>
+      </c>
+      <c r="C582" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="D582" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
       </c>
-      <c r="E582" s="1"/>
-      <c r="F582" s="1"/>
+      <c r="E582" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F582" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID")</f>
+        <v>DAVID</v>
+      </c>
       <c r="G582" s="1"/>
       <c r="H582" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01/2025")</f>
+        <v>01/2025</v>
       </c>
     </row>
     <row r="583">

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -503,40 +503,124 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="A9" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
+        <v>46032</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Shot ")</f>
+        <v>Shot </v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="D9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
+        <v>Fábio</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Caiu no chão ( estava agarrada uma na outra)")</f>
+        <v>Caiu no chão ( estava agarrada uma na outra)</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="A10" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
+        <v>46032</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
+        <v>Rúcula </v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"15g")</f>
+        <v>15g</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+      <c r="A11" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
+        <v>46032</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface")</f>
+        <v>Alface</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10g")</f>
+        <v>10g</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="A12" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
+        <v>46032</v>
+      </c>
+      <c r="B12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fatia de pão ")</f>
+        <v>Fatia de pão </v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Insumo")</f>
+        <v>Insumo</v>
+      </c>
+      <c r="D12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Partiu ao meio")</f>
+        <v>Partiu ao meio</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
@@ -1402,6 +1486,42 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
+    <row r="109">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -512,8 +512,8 @@
         <v>Shot </v>
       </c>
       <c r="C9" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
-        <v>Outro</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
       </c>
       <c r="D9" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -623,22 +623,64 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+      <c r="A13" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46033.0)</f>
+        <v>46033</v>
+      </c>
+      <c r="B13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo Shot")</f>
+        <v>Copo Shot</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jessyca")</f>
+        <v>Jessyca</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebrou na louça ")</f>
+        <v>Quebrou na louça </v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+      <c r="A14" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46033.0)</f>
+        <v>46033</v>
+      </c>
+      <c r="B14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Misto Quente(Sem presunto)")</f>
+        <v>Misto Quente(Sem presunto)</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="F14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alexandro")</f>
+        <v>Alexandro</v>
+      </c>
+      <c r="G14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente foi embora ")</f>
+        <v>Cliente foi embora </v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
@@ -1522,6 +1564,24 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
+    <row r="113">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -683,49 +683,154 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="A15" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
+        <v>46034</v>
+      </c>
+      <c r="B15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Petit Gateau")</f>
+        <v>Petit Gateau</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Vitrine).")</f>
+        <v>Venceu (Vitrine).</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="A16" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
+        <v>46034</v>
+      </c>
+      <c r="B16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mini Chocobrownie")</f>
+        <v>Mini Chocobrownie</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Vitrine).")</f>
+        <v>Venceu (Vitrine).</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="A17" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
+        <v>46034</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
+        <v>Rúcula </v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"158g")</f>
+        <v>158g</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas queimadas ")</f>
+        <v>Folhas queimadas </v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+      <c r="A18" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
+        <v>46034</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manjericão ")</f>
+        <v>Manjericão </v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"244g")</f>
+        <v>244g</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas queimadas ")</f>
+        <v>Folhas queimadas </v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
+      <c r="A19" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
+        <v>46034</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tomate cereja ")</f>
+        <v>Tomate cereja </v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"8g")</f>
+        <v>8g</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Murchou ")</f>
+        <v>Murchou </v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
@@ -1582,6 +1687,51 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
+    <row r="115">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -59,6 +59,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -688,8 +692,8 @@
         <v>46034</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Petit Gateau")</f>
-        <v>Petit Gateau</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mini Chocobrownie")</f>
+        <v>Mini Chocobrownie</v>
       </c>
       <c r="C15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
@@ -704,8 +708,8 @@
         <v>Venceu (Validade)</v>
       </c>
       <c r="F15" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
-        <v>David</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
       </c>
       <c r="G15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Vitrine).")</f>
@@ -718,16 +722,16 @@
         <v>46034</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mini Chocobrownie")</f>
-        <v>Mini Chocobrownie</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
+        <v>Rúcula </v>
       </c>
       <c r="C16" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
-        <v>Produto final</v>
-      </c>
-      <c r="D16" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"158g")</f>
+        <v>158g</v>
       </c>
       <c r="E16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
@@ -738,8 +742,8 @@
         <v>Jesiana</v>
       </c>
       <c r="G16" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Vitrine).")</f>
-        <v>Venceu (Vitrine).</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas queimadas ")</f>
+        <v>Folhas queimadas </v>
       </c>
     </row>
     <row r="17">
@@ -748,16 +752,16 @@
         <v>46034</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
-        <v>Rúcula </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manjericão ")</f>
+        <v>Manjericão </v>
       </c>
       <c r="C17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
       <c r="D17" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"158g")</f>
-        <v>158g</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"244g")</f>
+        <v>244g</v>
       </c>
       <c r="E17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
@@ -778,16 +782,16 @@
         <v>46034</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manjericão ")</f>
-        <v>Manjericão </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tomate cereja ")</f>
+        <v>Tomate cereja </v>
       </c>
       <c r="C18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
       <c r="D18" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"244g")</f>
-        <v>244g</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"8g")</f>
+        <v>8g</v>
       </c>
       <c r="E18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
@@ -798,48 +802,69 @@
         <v>Jesiana</v>
       </c>
       <c r="G18" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas queimadas ")</f>
-        <v>Folhas queimadas </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Murchou ")</f>
+        <v>Murchou </v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
-        <v>46034</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46035.0)</f>
+        <v>46035</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tomate cereja ")</f>
-        <v>Tomate cereja </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo Grande")</f>
+        <v>Copo Grande</v>
       </c>
       <c r="C19" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
-        <v>Hortifruti</v>
-      </c>
-      <c r="D19" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"8g")</f>
-        <v>8g</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="E19" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
-        <v>Venceu (Validade)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
       </c>
       <c r="F19" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
-        <v>Jesiana</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
       </c>
       <c r="G19" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Murchou ")</f>
-        <v>Murchou </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebrou na Louça ")</f>
+        <v>Quebrou na Louça </v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
+      <c r="A20" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46035.0)</f>
+        <v>46035</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Brigadeiro Pistache")</f>
+        <v>Brigadeiro Pistache</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
+        <v>Naiane</v>
+      </c>
+      <c r="G20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Deixou cair")</f>
+        <v>Deixou cair</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
@@ -1732,6 +1757,15 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
+    <row r="120">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -867,22 +867,64 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+      <c r="A21" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46038.0)</f>
+        <v>46038</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
+        <v>Rúcula </v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,024g")</f>
+        <v>0,024g</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Estragou ")</f>
+        <v>Estragou </v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+      <c r="A22" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46038.0)</f>
+        <v>46038</v>
+      </c>
+      <c r="B22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface ")</f>
+        <v>Alface </v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,031g")</f>
+        <v>0,031g</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas amareladas ")</f>
+        <v>Folhas amareladas </v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
@@ -1766,6 +1808,24 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
+    <row r="121">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -16,10 +16,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -43,12 +49,13 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -301,27 +308,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46024.0)</f>
         <v>46024</v>
       </c>
-      <c r="B2" s="1" t="str">
+      <c r="B2" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo pequeno")</f>
         <v>Copo pequeno</v>
       </c>
-      <c r="C2" s="1" t="str">
+      <c r="C2" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
         <v>Utensílio</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="str">
+      <c r="E2" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
         <v>Quebra</v>
       </c>
-      <c r="F2" s="1" t="str">
+      <c r="F2" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jaqueline")</f>
         <v>Jaqueline</v>
       </c>
-      <c r="G2" s="1" t="str">
+      <c r="G2" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Encontrado quebrado em baixo do caixa")</f>
         <v>Encontrado quebrado em baixo do caixa</v>
       </c>
@@ -331,27 +338,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46027.0)</f>
         <v>46027</v>
       </c>
-      <c r="B3" s="1" t="str">
+      <c r="B3" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo shot")</f>
         <v>Copo shot</v>
       </c>
-      <c r="C3" s="1" t="str">
+      <c r="C3" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
         <v>Utensílio</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="str">
+      <c r="E3" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
         <v>Quebra</v>
       </c>
-      <c r="F3" s="1" t="str">
+      <c r="F3" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jaqueline")</f>
         <v>Jaqueline</v>
       </c>
-      <c r="G3" s="1" t="str">
+      <c r="G3" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
         <v> </v>
       </c>
@@ -361,27 +368,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46029.0)</f>
         <v>46029</v>
       </c>
-      <c r="B4" s="1" t="str">
+      <c r="B4" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Taça de vinho")</f>
         <v>Taça de vinho</v>
       </c>
-      <c r="C4" s="1" t="str">
+      <c r="C4" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
         <v>Utensílio</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="str">
+      <c r="E4" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
         <v>Quebra</v>
       </c>
-      <c r="F4" s="1" t="str">
+      <c r="F4" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
         <v>David</v>
       </c>
-      <c r="G4" s="1" t="str">
+      <c r="G4" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebrou no manuseio")</f>
         <v>Quebrou no manuseio</v>
       </c>
@@ -391,27 +398,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46030.0)</f>
         <v>46030</v>
       </c>
-      <c r="B5" s="1" t="str">
+      <c r="B5" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo shot")</f>
         <v>Copo shot</v>
       </c>
-      <c r="C5" s="1" t="str">
+      <c r="C5" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
         <v>Utensílio</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="str">
+      <c r="E5" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
         <v>Quebra</v>
       </c>
-      <c r="F5" s="1" t="str">
+      <c r="F5" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jaqueline")</f>
         <v>Jaqueline</v>
       </c>
-      <c r="G5" s="1" t="str">
+      <c r="G5" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Lascado na borda ")</f>
         <v>Lascado na borda </v>
       </c>
@@ -421,27 +428,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46030.0)</f>
         <v>46030</v>
       </c>
-      <c r="B6" s="1" t="str">
+      <c r="B6" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface")</f>
         <v>Alface</v>
       </c>
-      <c r="C6" s="1" t="str">
+      <c r="C6" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D6" s="1" t="str">
+      <c r="D6" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"256g")</f>
         <v>256g</v>
       </c>
-      <c r="E6" s="1" t="str">
+      <c r="E6" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F6" s="1" t="str">
+      <c r="F6" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jaqueline")</f>
         <v>Jaqueline</v>
       </c>
-      <c r="G6" s="1" t="str">
+      <c r="G6" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas queimadas")</f>
         <v>Folhas queimadas</v>
       </c>
@@ -451,27 +458,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46030.0)</f>
         <v>46030</v>
       </c>
-      <c r="B7" s="1" t="str">
+      <c r="B7" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
         <v>Rúcula </v>
       </c>
-      <c r="C7" s="1" t="str">
+      <c r="C7" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D7" s="1" t="str">
+      <c r="D7" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"15g")</f>
         <v>15g</v>
       </c>
-      <c r="E7" s="1" t="str">
+      <c r="E7" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F7" s="1" t="str">
+      <c r="F7" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G7" s="1" t="str">
+      <c r="G7" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas amareladas")</f>
         <v>Folhas amareladas</v>
       </c>
@@ -481,27 +488,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46030.0)</f>
         <v>46030</v>
       </c>
-      <c r="B8" s="1" t="str">
+      <c r="B8" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tomate cereja")</f>
         <v>Tomate cereja</v>
       </c>
-      <c r="C8" s="1" t="str">
+      <c r="C8" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D8" s="1" t="str">
+      <c r="D8" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"15g")</f>
         <v>15g</v>
       </c>
-      <c r="E8" s="1" t="str">
+      <c r="E8" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F8" s="1" t="str">
+      <c r="F8" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G8" s="1" t="str">
+      <c r="G8" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vencido")</f>
         <v>Vencido</v>
       </c>
@@ -511,27 +518,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
         <v>46032</v>
       </c>
-      <c r="B9" s="1" t="str">
+      <c r="B9" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Shot ")</f>
         <v>Shot </v>
       </c>
-      <c r="C9" s="1" t="str">
+      <c r="C9" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
         <v>Utensílio</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="str">
+      <c r="E9" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
         <v>Quebra</v>
       </c>
-      <c r="F9" s="1" t="str">
+      <c r="F9" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
         <v>Fábio</v>
       </c>
-      <c r="G9" s="1" t="str">
+      <c r="G9" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Caiu no chão ( estava agarrada uma na outra)")</f>
         <v>Caiu no chão ( estava agarrada uma na outra)</v>
       </c>
@@ -541,27 +548,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
         <v>46032</v>
       </c>
-      <c r="B10" s="1" t="str">
+      <c r="B10" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
         <v>Rúcula </v>
       </c>
-      <c r="C10" s="1" t="str">
+      <c r="C10" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D10" s="1" t="str">
+      <c r="D10" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"15g")</f>
         <v>15g</v>
       </c>
-      <c r="E10" s="1" t="str">
+      <c r="E10" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F10" s="1" t="str">
+      <c r="F10" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G10" s="1" t="str">
+      <c r="G10" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
         <v> </v>
       </c>
@@ -571,27 +578,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
         <v>46032</v>
       </c>
-      <c r="B11" s="1" t="str">
+      <c r="B11" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface")</f>
         <v>Alface</v>
       </c>
-      <c r="C11" s="1" t="str">
+      <c r="C11" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D11" s="1" t="str">
+      <c r="D11" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10g")</f>
         <v>10g</v>
       </c>
-      <c r="E11" s="1" t="str">
+      <c r="E11" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F11" s="1" t="str">
+      <c r="F11" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G11" s="1" t="str">
+      <c r="G11" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
         <v> </v>
       </c>
@@ -601,27 +608,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
         <v>46032</v>
       </c>
-      <c r="B12" s="1" t="str">
+      <c r="B12" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fatia de pão ")</f>
         <v>Fatia de pão </v>
       </c>
-      <c r="C12" s="1" t="str">
+      <c r="C12" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Insumo")</f>
         <v>Insumo</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="str">
+      <c r="E12" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
         <v>Erro de processo</v>
       </c>
-      <c r="F12" s="1" t="str">
+      <c r="F12" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G12" s="1" t="str">
+      <c r="G12" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Partiu ao meio")</f>
         <v>Partiu ao meio</v>
       </c>
@@ -631,27 +638,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46033.0)</f>
         <v>46033</v>
       </c>
-      <c r="B13" s="1" t="str">
+      <c r="B13" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo Shot")</f>
         <v>Copo Shot</v>
       </c>
-      <c r="C13" s="1" t="str">
+      <c r="C13" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
         <v>Utensílio</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="str">
+      <c r="E13" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
         <v>Quebra</v>
       </c>
-      <c r="F13" s="1" t="str">
+      <c r="F13" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jessyca")</f>
         <v>Jessyca</v>
       </c>
-      <c r="G13" s="1" t="str">
+      <c r="G13" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebrou na louça ")</f>
         <v>Quebrou na louça </v>
       </c>
@@ -661,27 +668,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46033.0)</f>
         <v>46033</v>
       </c>
-      <c r="B14" s="1" t="str">
+      <c r="B14" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Misto Quente(Sem presunto)")</f>
         <v>Misto Quente(Sem presunto)</v>
       </c>
-      <c r="C14" s="1" t="str">
+      <c r="C14" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
         <v>Produto final</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E14" s="1" t="str">
+      <c r="E14" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente")</f>
         <v>Cliente</v>
       </c>
-      <c r="F14" s="1" t="str">
+      <c r="F14" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alexandro")</f>
         <v>Alexandro</v>
       </c>
-      <c r="G14" s="1" t="str">
+      <c r="G14" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente foi embora ")</f>
         <v>Cliente foi embora </v>
       </c>
@@ -691,27 +698,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
         <v>46034</v>
       </c>
-      <c r="B15" s="1" t="str">
+      <c r="B15" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mini Chocobrownie")</f>
         <v>Mini Chocobrownie</v>
       </c>
-      <c r="C15" s="1" t="str">
+      <c r="C15" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
         <v>Produto final</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="1" t="str">
+      <c r="E15" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F15" s="1" t="str">
+      <c r="F15" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G15" s="1" t="str">
+      <c r="G15" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Vitrine).")</f>
         <v>Venceu (Vitrine).</v>
       </c>
@@ -721,27 +728,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
         <v>46034</v>
       </c>
-      <c r="B16" s="1" t="str">
+      <c r="B16" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
         <v>Rúcula </v>
       </c>
-      <c r="C16" s="1" t="str">
+      <c r="C16" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D16" s="1" t="str">
+      <c r="D16" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"158g")</f>
         <v>158g</v>
       </c>
-      <c r="E16" s="1" t="str">
+      <c r="E16" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F16" s="1" t="str">
+      <c r="F16" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G16" s="1" t="str">
+      <c r="G16" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas queimadas ")</f>
         <v>Folhas queimadas </v>
       </c>
@@ -751,27 +758,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
         <v>46034</v>
       </c>
-      <c r="B17" s="1" t="str">
+      <c r="B17" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manjericão ")</f>
         <v>Manjericão </v>
       </c>
-      <c r="C17" s="1" t="str">
+      <c r="C17" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D17" s="1" t="str">
+      <c r="D17" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"244g")</f>
         <v>244g</v>
       </c>
-      <c r="E17" s="1" t="str">
+      <c r="E17" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F17" s="1" t="str">
+      <c r="F17" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G17" s="1" t="str">
+      <c r="G17" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas queimadas ")</f>
         <v>Folhas queimadas </v>
       </c>
@@ -781,27 +788,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
         <v>46034</v>
       </c>
-      <c r="B18" s="1" t="str">
+      <c r="B18" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tomate cereja ")</f>
         <v>Tomate cereja </v>
       </c>
-      <c r="C18" s="1" t="str">
+      <c r="C18" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D18" s="1" t="str">
+      <c r="D18" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"8g")</f>
         <v>8g</v>
       </c>
-      <c r="E18" s="1" t="str">
+      <c r="E18" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F18" s="1" t="str">
+      <c r="F18" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G18" s="1" t="str">
+      <c r="G18" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Murchou ")</f>
         <v>Murchou </v>
       </c>
@@ -811,27 +818,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46035.0)</f>
         <v>46035</v>
       </c>
-      <c r="B19" s="1" t="str">
+      <c r="B19" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo Grande")</f>
         <v>Copo Grande</v>
       </c>
-      <c r="C19" s="1" t="str">
+      <c r="C19" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
         <v>Utensílio</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E19" s="1" t="str">
+      <c r="E19" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
         <v>Quebra</v>
       </c>
-      <c r="F19" s="1" t="str">
+      <c r="F19" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
         <v>David</v>
       </c>
-      <c r="G19" s="1" t="str">
+      <c r="G19" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebrou na Louça ")</f>
         <v>Quebrou na Louça </v>
       </c>
@@ -841,27 +848,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46035.0)</f>
         <v>46035</v>
       </c>
-      <c r="B20" s="1" t="str">
+      <c r="B20" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Brigadeiro Pistache")</f>
         <v>Brigadeiro Pistache</v>
       </c>
-      <c r="C20" s="1" t="str">
+      <c r="C20" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
         <v>Produto final</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E20" s="1" t="str">
+      <c r="E20" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
         <v>Erro de processo</v>
       </c>
-      <c r="F20" s="1" t="str">
+      <c r="F20" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
         <v>Naiane</v>
       </c>
-      <c r="G20" s="1" t="str">
+      <c r="G20" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Deixou cair")</f>
         <v>Deixou cair</v>
       </c>
@@ -871,27 +878,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46038.0)</f>
         <v>46038</v>
       </c>
-      <c r="B21" s="1" t="str">
+      <c r="B21" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
         <v>Rúcula </v>
       </c>
-      <c r="C21" s="1" t="str">
+      <c r="C21" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D21" s="1" t="str">
+      <c r="D21" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,024g")</f>
         <v>0,024g</v>
       </c>
-      <c r="E21" s="1" t="str">
+      <c r="E21" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F21" s="1" t="str">
+      <c r="F21" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G21" s="1" t="str">
+      <c r="G21" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Estragou ")</f>
         <v>Estragou </v>
       </c>
@@ -901,930 +908,960 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46038.0)</f>
         <v>46038</v>
       </c>
-      <c r="B22" s="1" t="str">
+      <c r="B22" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface ")</f>
         <v>Alface </v>
       </c>
-      <c r="C22" s="1" t="str">
+      <c r="C22" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
         <v>Hortifruti</v>
       </c>
-      <c r="D22" s="1" t="str">
+      <c r="D22" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,031g")</f>
         <v>0,031g</v>
       </c>
-      <c r="E22" s="1" t="str">
+      <c r="E22" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
         <v>Venceu (Validade)</v>
       </c>
-      <c r="F22" s="1" t="str">
+      <c r="F22" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="G22" s="1" t="str">
+      <c r="G22" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Folhas amareladas ")</f>
         <v>Folhas amareladas </v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
+      <c r="A23" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46039.0)</f>
+        <v>46039</v>
+      </c>
+      <c r="B23" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cheesecake")</f>
+        <v>Cheesecake</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D23" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E23" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
+        <v>Naiane</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muito Tempo recuada ")</f>
+        <v>Muito Tempo recuada </v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
     </row>
     <row r="25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
     </row>
     <row r="26">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
     </row>
     <row r="27">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
     </row>
     <row r="28">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
     </row>
     <row r="29">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
     </row>
     <row r="30">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
     </row>
     <row r="31">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
     </row>
     <row r="32">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
     </row>
     <row r="33">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
     </row>
     <row r="34">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
     </row>
     <row r="35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
     </row>
     <row r="36">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
     </row>
     <row r="37">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
     </row>
     <row r="38">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
     </row>
     <row r="39">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
     </row>
     <row r="40">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
     </row>
     <row r="41">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
     </row>
     <row r="42">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
     </row>
     <row r="43">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
     </row>
     <row r="44">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
     </row>
     <row r="45">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
     </row>
     <row r="46">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
     </row>
     <row r="47">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
     </row>
     <row r="48">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
     </row>
     <row r="49">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
     </row>
     <row r="50">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
     </row>
     <row r="51">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
     </row>
     <row r="52">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
     </row>
     <row r="53">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
     </row>
     <row r="54">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
     </row>
     <row r="55">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
     </row>
     <row r="56">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
     </row>
     <row r="57">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
     </row>
     <row r="58">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
     </row>
     <row r="59">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
     </row>
     <row r="60">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
     </row>
     <row r="61">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
     </row>
     <row r="62">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
     </row>
     <row r="63">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
     </row>
     <row r="64">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
     </row>
     <row r="65">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
     </row>
     <row r="66">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
     </row>
     <row r="67">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
     </row>
     <row r="68">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
     </row>
     <row r="69">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
     </row>
     <row r="70">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
     </row>
     <row r="71">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
     </row>
     <row r="72">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
     </row>
     <row r="73">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
     </row>
     <row r="74">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
     </row>
     <row r="75">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
     </row>
     <row r="76">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
     </row>
     <row r="77">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
     </row>
     <row r="78">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
     </row>
     <row r="79">
-      <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
     </row>
     <row r="80">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
     </row>
     <row r="81">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
     </row>
     <row r="82">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
     </row>
     <row r="83">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
     </row>
     <row r="84">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
     </row>
     <row r="85">
-      <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
     </row>
     <row r="86">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
     </row>
     <row r="87">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
     </row>
     <row r="88">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
     </row>
     <row r="89">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
     </row>
     <row r="90">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
     </row>
     <row r="91">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
     </row>
     <row r="92">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
     </row>
     <row r="93">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
     </row>
     <row r="94">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
     </row>
     <row r="95">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
     </row>
     <row r="96">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
     </row>
     <row r="97">
-      <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
     </row>
     <row r="98">
-      <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
     </row>
     <row r="99">
-      <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
     </row>
     <row r="100">
-      <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
     </row>
     <row r="101">
-      <c r="A101" s="1"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
     </row>
     <row r="102">
-      <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
     </row>
     <row r="103">
-      <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
     </row>
     <row r="104">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
     </row>
     <row r="105">
-      <c r="A105" s="1"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
     </row>
     <row r="106">
-      <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
     </row>
     <row r="107">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
     </row>
     <row r="108">
-      <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
     </row>
     <row r="109">
-      <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
     </row>
     <row r="110">
-      <c r="A110" s="1"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
     </row>
     <row r="111">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
     </row>
     <row r="112">
-      <c r="A112" s="1"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
     </row>
     <row r="113">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
     </row>
     <row r="114">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
     </row>
     <row r="115">
-      <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
     </row>
     <row r="116">
-      <c r="A116" s="1"/>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
     </row>
     <row r="117">
-      <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
     </row>
     <row r="118">
-      <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
     </row>
     <row r="119">
-      <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-      <c r="E119" s="1"/>
-      <c r="F119" s="1"/>
-      <c r="G119" s="1"/>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
     </row>
     <row r="120">
-      <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
     </row>
     <row r="121">
-      <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
-      <c r="F121" s="1"/>
-      <c r="G121" s="1"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
     </row>
     <row r="122">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -964,13 +964,34 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="A24" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46040.0)</f>
+        <v>46040</v>
+      </c>
+      <c r="B24" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolo de laranja ")</f>
+        <v>Bolo de laranja </v>
+      </c>
+      <c r="C24" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D24" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="E24" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F24" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alex")</f>
+        <v>Alex</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cortado errado")</f>
+        <v>Cortado errado</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3"/>
@@ -1863,6 +1884,15 @@
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
     </row>
+    <row r="124">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -994,22 +994,64 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+      <c r="A25" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46040.0)</f>
+        <v>46040</v>
+      </c>
+      <c r="B25" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo grande ")</f>
+        <v>Copo grande </v>
+      </c>
+      <c r="C25" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D25" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F25" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Gabriela")</f>
+        <v>Gabriela</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Deixou cair ")</f>
+        <v>Deixou cair </v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="A26" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46040.0)</f>
+        <v>46040</v>
+      </c>
+      <c r="B26" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Xícara pequena café ")</f>
+        <v>Xícara pequena café </v>
+      </c>
+      <c r="C26" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D26" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F26" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Gabriela")</f>
+        <v>Gabriela</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Deixou cair ")</f>
+        <v>Deixou cair </v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3"/>
@@ -1893,6 +1935,24 @@
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
     </row>
+    <row r="125">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1054,49 +1054,154 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="A27" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Leite")</f>
+        <v>Leite</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"100 ml")</f>
+        <v>100 ml</v>
+      </c>
+      <c r="E27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
+        <v>Fábio</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo escorregou no pó de café ")</f>
+        <v>Copo escorregou no pó de café </v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="A28" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Blend")</f>
+        <v>Blend</v>
+      </c>
+      <c r="C28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10g")</f>
+        <v>10g</v>
+      </c>
+      <c r="E28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jaqueline")</f>
+        <v>Jaqueline</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Derrubou no balcão ")</f>
+        <v>Derrubou no balcão </v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="A29" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Shot ")</f>
+        <v>Shot </v>
+      </c>
+      <c r="C29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D29" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fátima")</f>
+        <v>Fátima</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="A30" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"rúcula ")</f>
+        <v>rúcula </v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"20g")</f>
+        <v>20g</v>
+      </c>
+      <c r="E30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="A31" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface ")</f>
+        <v>Alface </v>
+      </c>
+      <c r="C31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"28g")</f>
+        <v>28g</v>
+      </c>
+      <c r="E31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3"/>
@@ -1953,6 +2058,51 @@
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
     </row>
+    <row r="127">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1054,67 +1054,214 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="A27" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Leite")</f>
+        <v>Leite</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"100 ml")</f>
+        <v>100 ml</v>
+      </c>
+      <c r="E27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
+        <v>Fábio</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo escorregou no pó de café ")</f>
+        <v>Copo escorregou no pó de café </v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="A28" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Blend")</f>
+        <v>Blend</v>
+      </c>
+      <c r="C28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10g")</f>
+        <v>10g</v>
+      </c>
+      <c r="E28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jaqueline")</f>
+        <v>Jaqueline</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Derrubou no balcão ")</f>
+        <v>Derrubou no balcão </v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="A29" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Shot ")</f>
+        <v>Shot </v>
+      </c>
+      <c r="C29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D29" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fátima")</f>
+        <v>Fátima</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="A30" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"rúcula ")</f>
+        <v>rúcula </v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"20g")</f>
+        <v>20g</v>
+      </c>
+      <c r="E30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="A31" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface ")</f>
+        <v>Alface </v>
+      </c>
+      <c r="C31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"28g")</f>
+        <v>28g</v>
+      </c>
+      <c r="E31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="A32" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
+        <v>46043</v>
+      </c>
+      <c r="B32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prato Sobremesa")</f>
+        <v>Prato Sobremesa</v>
+      </c>
+      <c r="C32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D32" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Deixou cair.")</f>
+        <v>Deixou cair.</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="A33" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
+        <v>46043</v>
+      </c>
+      <c r="B33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolo Fubá ")</f>
+        <v>Bolo Fubá </v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D33" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Deixou cair.")</f>
+        <v>Deixou cair.</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3"/>
@@ -1953,6 +2100,69 @@
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
     </row>
+    <row r="127">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1204,58 +1204,184 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="A32" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
+        <v>46043</v>
+      </c>
+      <c r="B32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prato Sobremesa")</f>
+        <v>Prato Sobremesa</v>
+      </c>
+      <c r="C32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D32" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Deixou cair.")</f>
+        <v>Deixou cair.</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="A33" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
+        <v>46043</v>
+      </c>
+      <c r="B33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolo Fubá ")</f>
+        <v>Bolo Fubá </v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D33" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G33" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Deixou cair.")</f>
+        <v>Deixou cair.</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+      <c r="A34" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
+        <v>46044</v>
+      </c>
+      <c r="B34" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Salsa ")</f>
+        <v>Salsa </v>
+      </c>
+      <c r="C34" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D34" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,160g")</f>
+        <v>0,160g</v>
+      </c>
+      <c r="E34" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F34" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G34" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="A35" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
+        <v>46044</v>
+      </c>
+      <c r="B35" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface ")</f>
+        <v>Alface </v>
+      </c>
+      <c r="C35" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D35" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,120g")</f>
+        <v>0,120g</v>
+      </c>
+      <c r="E35" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F35" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G35" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+      <c r="A36" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
+        <v>46044</v>
+      </c>
+      <c r="B36" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
+        <v>Rúcula </v>
+      </c>
+      <c r="C36" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D36" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,081g")</f>
+        <v>0,081g</v>
+      </c>
+      <c r="E36" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F36" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G36" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+      <c r="A37" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
+        <v>46044</v>
+      </c>
+      <c r="B37" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bacon ")</f>
+        <v>Bacon </v>
+      </c>
+      <c r="C37" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="D37" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,105g")</f>
+        <v>0,105g</v>
+      </c>
+      <c r="E37" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F37" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G37" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3"/>
@@ -2103,6 +2229,60 @@
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
     </row>
+    <row r="132">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1384,13 +1384,34 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+      <c r="A38" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46045.0)</f>
+        <v>46045</v>
+      </c>
+      <c r="B38" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Torta Cheesecake")</f>
+        <v>Torta Cheesecake</v>
+      </c>
+      <c r="C38" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D38" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="E38" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="F38" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G38" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente reclamou de estar ruim")</f>
+        <v>Cliente reclamou de estar ruim</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3"/>
@@ -2283,6 +2304,15 @@
       <c r="F137" s="3"/>
       <c r="G137" s="3"/>
     </row>
+    <row r="138">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1414,13 +1414,34 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="A39" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46047.0)</f>
+        <v>46047</v>
+      </c>
+      <c r="B39" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prato de Sobremesa ")</f>
+        <v>Prato de Sobremesa </v>
+      </c>
+      <c r="C39" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D39" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F39" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G39" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Caiu")</f>
+        <v>Caiu</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3"/>
@@ -2313,6 +2334,15 @@
       <c r="F138" s="3"/>
       <c r="G138" s="3"/>
     </row>
+    <row r="139">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1444,13 +1444,34 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+      <c r="A40" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46049.0)</f>
+        <v>46049</v>
+      </c>
+      <c r="B40" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pão Ciabatta ")</f>
+        <v>Pão Ciabatta </v>
+      </c>
+      <c r="C40" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D40" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1/2")</f>
+        <v>1/2</v>
+      </c>
+      <c r="E40" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F40" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
+        <v>Naiane</v>
+      </c>
+      <c r="G40" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Queimou")</f>
+        <v>Queimou</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3"/>
@@ -2343,6 +2364,15 @@
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
     </row>
+    <row r="140">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1474,40 +1474,124 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="A41" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
+        <v>46051</v>
+      </c>
+      <c r="B41" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Torta Palmito")</f>
+        <v>Torta Palmito</v>
+      </c>
+      <c r="C41" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D41" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F41" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
+        <v>Naiane</v>
+      </c>
+      <c r="G41" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebrou no meio ")</f>
+        <v>Quebrou no meio </v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+      <c r="A42" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
+        <v>46051</v>
+      </c>
+      <c r="B42" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"latte duplo")</f>
+        <v>latte duplo</v>
+      </c>
+      <c r="C42" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D42" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="F42" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
+        <v>Fábio</v>
+      </c>
+      <c r="G42" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente alegou que prefere com café descafeinado. Orientamos o cliente.")</f>
+        <v>Cliente alegou que prefere com café descafeinado. Orientamos o cliente.</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
+      <c r="A43" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
+        <v>46051</v>
+      </c>
+      <c r="B43" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo Shot")</f>
+        <v>Copo Shot</v>
+      </c>
+      <c r="C43" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D43" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E43" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F43" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G43" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebrou ")</f>
+        <v>Quebrou </v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="A44" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
+        <v>46051</v>
+      </c>
+      <c r="B44" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prato Sobremesa")</f>
+        <v>Prato Sobremesa</v>
+      </c>
+      <c r="C44" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D44" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E44" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F44" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G44" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebrou")</f>
+        <v>Quebrou</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3"/>
@@ -2373,6 +2457,42 @@
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
     </row>
+    <row r="141">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1594,31 +1594,94 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+      <c r="A45" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46052.0)</f>
+        <v>46052</v>
+      </c>
+      <c r="B45" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
+        <v>Rúcula </v>
+      </c>
+      <c r="C45" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D45" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,017g")</f>
+        <v>0,017g</v>
+      </c>
+      <c r="E45" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F45" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G45" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
+      <c r="A46" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46052.0)</f>
+        <v>46052</v>
+      </c>
+      <c r="B46" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface ")</f>
+        <v>Alface </v>
+      </c>
+      <c r="C46" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D46" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,255g")</f>
+        <v>0,255g</v>
+      </c>
+      <c r="E46" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F46" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G46" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
+      <c r="A47" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46052.0)</f>
+        <v>46052</v>
+      </c>
+      <c r="B47" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Molheira ")</f>
+        <v>Molheira </v>
+      </c>
+      <c r="C47" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D47" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E47" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F47" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G47" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3"/>
@@ -2493,6 +2556,33 @@
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
     </row>
+    <row r="145">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1684,13 +1684,34 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="A48" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46053.0)</f>
+        <v>46053</v>
+      </c>
+      <c r="B48" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arroz arbóreo")</f>
+        <v>Arroz arbóreo</v>
+      </c>
+      <c r="C48" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Insumo")</f>
+        <v>Insumo</v>
+      </c>
+      <c r="D48" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E48" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F48" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Brunna")</f>
+        <v>Brunna</v>
+      </c>
+      <c r="G48" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Aspecto fora do padrão de qualidade")</f>
+        <v>Aspecto fora do padrão de qualidade</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3"/>
@@ -2583,6 +2604,15 @@
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
     </row>
+    <row r="148">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1714,49 +1714,154 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+      <c r="A49" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46056.0)</f>
+        <v>46056</v>
+      </c>
+      <c r="B49" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Torta cheesecake ")</f>
+        <v>Torta cheesecake </v>
+      </c>
+      <c r="C49" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D49" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E49" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F49" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
+        <v>Fábio</v>
+      </c>
+      <c r="G49" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Estragou")</f>
+        <v>Estragou</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
+      <c r="A50" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B50" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Soda italiana framboesa ")</f>
+        <v>Soda italiana framboesa </v>
+      </c>
+      <c r="C50" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D50" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E50" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="F50" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
+        <v>Fábio</v>
+      </c>
+      <c r="G50" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente pediu de framboesa e depois pediu para trocar de sabor ")</f>
+        <v>Cliente pediu de framboesa e depois pediu para trocar de sabor </v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+      <c r="A51" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B51" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Empada palmito ")</f>
+        <v>Empada palmito </v>
+      </c>
+      <c r="C51" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D51" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E51" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="F51" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
+        <v>Fábio</v>
+      </c>
+      <c r="G51" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente falou que era de frango, mesmo sendo explicado que era de palmito ela não quis ")</f>
+        <v>Cliente falou que era de frango, mesmo sendo explicado que era de palmito ela não quis </v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
+      <c r="A52" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B52" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo pequeno ")</f>
+        <v>Copo pequeno </v>
+      </c>
+      <c r="C52" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D52" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E52" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F52" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fátima")</f>
+        <v>Fátima</v>
+      </c>
+      <c r="G52" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Escorregou da mão ")</f>
+        <v>Escorregou da mão </v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
+      <c r="A53" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B53" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Caldo verde ")</f>
+        <v>Caldo verde </v>
+      </c>
+      <c r="C53" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D53" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="E53" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F53" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
+        <v>Fábio</v>
+      </c>
+      <c r="G53" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Data vencida")</f>
+        <v>Data vencida</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3"/>
@@ -2613,6 +2718,51 @@
       <c r="F148" s="3"/>
       <c r="G148" s="3"/>
     </row>
+    <row r="149">
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1864,13 +1864,34 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
+      <c r="A54" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46058.0)</f>
+        <v>46058</v>
+      </c>
+      <c r="B54" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," caneca nadir de alça ")</f>
+        <v> caneca nadir de alça </v>
+      </c>
+      <c r="C54" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D54" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E54" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F54" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jaqueline")</f>
+        <v>Jaqueline</v>
+      </c>
+      <c r="G54" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cliente pediu gelo pra colocar junto com o café trincou a caneca ")</f>
+        <v>Cliente pediu gelo pra colocar junto com o café trincou a caneca </v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3"/>
@@ -2763,6 +2784,15 @@
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
     </row>
+    <row r="154">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -1894,49 +1894,154 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
+      <c r="A55" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46062.0)</f>
+        <v>46062</v>
+      </c>
+      <c r="B55" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"latte simples")</f>
+        <v>latte simples</v>
+      </c>
+      <c r="C55" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D55" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E55" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F55" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fátima")</f>
+        <v>Fátima</v>
+      </c>
+      <c r="G55" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"fez com o leite errado.")</f>
+        <v>fez com o leite errado.</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
+      <c r="A56" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46062.0)</f>
+        <v>46062</v>
+      </c>
+      <c r="B56" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"xicara pequena")</f>
+        <v>xicara pequena</v>
+      </c>
+      <c r="C56" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D56" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E56" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F56" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
+        <v>Fábio</v>
+      </c>
+      <c r="G56" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"alça quebrou na minha mao")</f>
+        <v>alça quebrou na minha mao</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
+      <c r="A57" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46062.0)</f>
+        <v>46062</v>
+      </c>
+      <c r="B57" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manjericão ")</f>
+        <v>Manjericão </v>
+      </c>
+      <c r="C57" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D57" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,320g")</f>
+        <v>0,320g</v>
+      </c>
+      <c r="E57" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F57" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G57" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
+      <c r="A58" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46061.0)</f>
+        <v>46061</v>
+      </c>
+      <c r="B58" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tomate")</f>
+        <v>Tomate</v>
+      </c>
+      <c r="C58" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D58" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"35g")</f>
+        <v>35g</v>
+      </c>
+      <c r="E58" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F58" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
+        <v>Naiane</v>
+      </c>
+      <c r="G58" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Estragado")</f>
+        <v>Estragado</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
+      <c r="A59" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46061.0)</f>
+        <v>46061</v>
+      </c>
+      <c r="B59" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ovo")</f>
+        <v>Ovo</v>
+      </c>
+      <c r="C59" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Insumo")</f>
+        <v>Insumo</v>
+      </c>
+      <c r="D59" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E59" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F59" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
+        <v>Naiane</v>
+      </c>
+      <c r="G59" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Estragado")</f>
+        <v>Estragado</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3"/>
@@ -2793,6 +2898,51 @@
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
     </row>
+    <row r="155">
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -2044,22 +2044,64 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
+      <c r="A60" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46063.0)</f>
+        <v>46063</v>
+      </c>
+      <c r="B60" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matcha Gelado")</f>
+        <v>Matcha Gelado</v>
+      </c>
+      <c r="C60" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D60" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E60" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Erro de processo")</f>
+        <v>Erro de processo</v>
+      </c>
+      <c r="F60" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"David")</f>
+        <v>David</v>
+      </c>
+      <c r="G60" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fez errado ")</f>
+        <v>Fez errado </v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
+      <c r="A61" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46063.0)</f>
+        <v>46063</v>
+      </c>
+      <c r="B61" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
+        <v>Rúcula </v>
+      </c>
+      <c r="C61" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D61" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07)</f>
+        <v>0.07</v>
+      </c>
+      <c r="E61" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F61" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
+        <v>Naiane</v>
+      </c>
+      <c r="G61" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Amarelado")</f>
+        <v>Amarelado</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3"/>
@@ -2943,6 +2985,24 @@
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
     </row>
+    <row r="160">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="3"/>
+      <c r="G161" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -2104,49 +2104,154 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
+      <c r="A62" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46064.0)</f>
+        <v>46064</v>
+      </c>
+      <c r="B62" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Espresso simples")</f>
+        <v>Espresso simples</v>
+      </c>
+      <c r="C62" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D62" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E62" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Lançamento errado")</f>
+        <v>Lançamento errado</v>
+      </c>
+      <c r="F62" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fátima")</f>
+        <v>Fátima</v>
+      </c>
+      <c r="G62" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
+      <c r="A63" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46064.0)</f>
+        <v>46064</v>
+      </c>
+      <c r="B63" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Latte simples")</f>
+        <v>Latte simples</v>
+      </c>
+      <c r="C63" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Produto final")</f>
+        <v>Produto final</v>
+      </c>
+      <c r="D63" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E63" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Lançamento errado")</f>
+        <v>Lançamento errado</v>
+      </c>
+      <c r="F63" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fátima")</f>
+        <v>Fátima</v>
+      </c>
+      <c r="G63" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
+      <c r="A64" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46064.0)</f>
+        <v>46064</v>
+      </c>
+      <c r="B64" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface")</f>
+        <v>Alface</v>
+      </c>
+      <c r="C64" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D64" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"290g")</f>
+        <v>290g</v>
+      </c>
+      <c r="E64" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F64" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G64" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
+      <c r="A65" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46064.0)</f>
+        <v>46064</v>
+      </c>
+      <c r="B65" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula")</f>
+        <v>Rúcula</v>
+      </c>
+      <c r="C65" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D65" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"61g")</f>
+        <v>61g</v>
+      </c>
+      <c r="E65" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F65" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G65" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
+      <c r="A66" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46064.0)</f>
+        <v>46064</v>
+      </c>
+      <c r="B66" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ovo")</f>
+        <v>Ovo</v>
+      </c>
+      <c r="C66" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Insumo")</f>
+        <v>Insumo</v>
+      </c>
+      <c r="D66" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E66" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F66" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G66" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Podre")</f>
+        <v>Podre</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3"/>
@@ -3003,6 +3108,51 @@
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
     </row>
+    <row r="162">
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="3"/>
+      <c r="F162" s="3"/>
+      <c r="G162" s="3"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="3"/>
+      <c r="F163" s="3"/>
+      <c r="G163" s="3"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3"/>
+      <c r="G165" s="3"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -2254,22 +2254,64 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
+      <c r="A67" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46067.0)</f>
+        <v>46067</v>
+      </c>
+      <c r="B67" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface")</f>
+        <v>Alface</v>
+      </c>
+      <c r="C67" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D67" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.14)</f>
+        <v>0.14</v>
+      </c>
+      <c r="E67" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F67" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G67" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Amarelada")</f>
+        <v>Amarelada</v>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
+      <c r="A68" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46067.0)</f>
+        <v>46067</v>
+      </c>
+      <c r="B68" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manjericão ")</f>
+        <v>Manjericão </v>
+      </c>
+      <c r="C68" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D68" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.03)</f>
+        <v>0.03</v>
+      </c>
+      <c r="E68" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F68" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G68" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ruim")</f>
+        <v>Ruim</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3"/>
@@ -3153,6 +3195,24 @@
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
     </row>
+    <row r="167">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="3"/>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="3"/>
+      <c r="F168" s="3"/>
+      <c r="G168" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -2314,22 +2314,64 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
+      <c r="A69" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46068.0)</f>
+        <v>46068</v>
+      </c>
+      <c r="B69" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rúcula ")</f>
+        <v>Rúcula </v>
+      </c>
+      <c r="C69" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D69" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,121g")</f>
+        <v>0,121g</v>
+      </c>
+      <c r="E69" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F69" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G69" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
+      <c r="A70" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46068.0)</f>
+        <v>46068</v>
+      </c>
+      <c r="B70" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alface ")</f>
+        <v>Alface </v>
+      </c>
+      <c r="C70" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D70" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0,083g")</f>
+        <v>0,083g</v>
+      </c>
+      <c r="E70" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F70" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G70" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3"/>
@@ -3213,6 +3255,24 @@
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
     </row>
+    <row r="169">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="3"/>
+      <c r="F169" s="3"/>
+      <c r="G169" s="3"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="3"/>
+      <c r="G170" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -2374,13 +2374,34 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
+      <c r="A71" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46069.0)</f>
+        <v>46069</v>
+      </c>
+      <c r="B71" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Copo Grande")</f>
+        <v>Copo Grande</v>
+      </c>
+      <c r="C71" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Utensílio")</f>
+        <v>Utensílio</v>
+      </c>
+      <c r="D71" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E71" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebra")</f>
+        <v>Quebra</v>
+      </c>
+      <c r="F71" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alex")</f>
+        <v>Alex</v>
+      </c>
+      <c r="G71" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Quebrou na pia ")</f>
+        <v>Quebrou na pia </v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3"/>
@@ -3273,6 +3294,15 @@
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
     </row>
+    <row r="171">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="3"/>
+      <c r="F171" s="3"/>
+      <c r="G171" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -2404,13 +2404,34 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
+      <c r="A72" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46070.0)</f>
+        <v>46070</v>
+      </c>
+      <c r="B72" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cheesecake ")</f>
+        <v>Cheesecake </v>
+      </c>
+      <c r="C72" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Outro")</f>
+        <v>Outro</v>
+      </c>
+      <c r="D72" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="E72" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F72" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
+        <v>Jesiana</v>
+      </c>
+      <c r="G72" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N")</f>
+        <v>N</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3"/>
@@ -3303,6 +3324,15 @@
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
     </row>
+    <row r="172">
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/base_cinema_perdas.xlsx
+++ b/base_cinema_perdas.xlsx
@@ -2434,13 +2434,34 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
+      <c r="A73" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46071.0)</f>
+        <v>46071</v>
+      </c>
+      <c r="B73" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tomate Cereja")</f>
+        <v>Tomate Cereja</v>
+      </c>
+      <c r="C73" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hortifruti")</f>
+        <v>Hortifruti</v>
+      </c>
+      <c r="D73" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.114)</f>
+        <v>0.114</v>
+      </c>
+      <c r="E73" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Venceu (Validade)")</f>
+        <v>Venceu (Validade)</v>
+      </c>
+      <c r="F73" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
+        <v>Naiane</v>
+      </c>
+      <c r="G73" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Estragou")</f>
+        <v>Estragou</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3"/>
@@ -3333,6 +3354,15 @@
       <c r="F172" s="3"/>
       <c r="G172" s="3"/>
     </row>
+    <row r="173">
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
